--- a/excel/dosyalar/ayo_cost_excel.xlsx
+++ b/excel/dosyalar/ayo_cost_excel.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="456" yWindow="1536" windowWidth="22584" windowHeight="10596" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="creditcard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="travel" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="wage" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="sample" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="other" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="fuil" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="meal" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="[$₺-41F]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +41,17 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -56,13 +66,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFCC6600"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -94,11 +98,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -108,17 +109,14 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -126,74 +124,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -468,217 +399,217 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.77734375" defaultRowHeight="20.4" customHeight="1"/>
   <sheetData>
     <row r="1" ht="20.4" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>MONTH</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>COST (TL)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>COST(USD)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20.4" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>11811.33</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>393.06</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>30.05</v>
+      <c r="B2" s="2" t="n">
+        <v>34917.15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>980.8200000000001</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>35.6</v>
       </c>
     </row>
     <row r="3" ht="20.4" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>32375.64</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1054.58</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>30.7</v>
+      <c r="B3" s="2" t="n">
+        <v>47882.2</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1321.25</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>36.24</v>
       </c>
     </row>
     <row r="4" ht="20.4" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>30456.84</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>948.22</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>32.12</v>
+      <c r="B4" s="2" t="n">
+        <v>55850.23</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1507.02</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>37.06</v>
       </c>
     </row>
     <row r="5" ht="20.4" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>38414.37</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1185.63</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>32.4</v>
+      <c r="B5" s="2" t="n">
+        <v>36922.14</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>969.59</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>38.08</v>
       </c>
     </row>
     <row r="6" ht="20.4" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>15541.48</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>482.21</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>32.23</v>
+      <c r="B6" s="2" t="n">
+        <v>20433.28</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>528.26</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>38.68</v>
       </c>
     </row>
     <row r="7" ht="20.4" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>June</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>44056.3</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1357.25</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>32.46</v>
+      <c r="B7" s="2" t="n">
+        <v>22888.13</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>579.15</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>39.52</v>
       </c>
     </row>
     <row r="8" ht="20.4" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>21149.99</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>640.13</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>33.04</v>
+      <c r="B8" s="2" t="n">
+        <v>15129.18</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>375.69</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>40.27</v>
       </c>
     </row>
     <row r="9" ht="20.4" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>August</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>33.58</v>
+      <c r="B9" s="2" t="n">
+        <v>15129.18</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>370.09</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>40.88</v>
       </c>
     </row>
     <row r="10" ht="20.4" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>September</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
+      <c r="B10" s="2" t="n">
+        <v>34581.15</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>838.13</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>41.26</v>
       </c>
     </row>
     <row r="11" ht="20.4" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="n">
+        <v>20278.94</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>486.19</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>41.71</v>
       </c>
     </row>
     <row r="12" ht="20.4" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
+      <c r="B12" s="2" t="n">
+        <v>26339.37</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>622.09</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>42.34</v>
       </c>
     </row>
     <row r="13" ht="20.4" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>December</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
+      <c r="B13" s="2" t="n">
+        <v>33982.81</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>794.92</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>42.75</v>
       </c>
     </row>
     <row r="14" ht="20.4" customHeight="1">
@@ -688,12 +619,12 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>193805.95</v>
+        <v>364333.76</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>6061.08</v>
-      </c>
-      <c r="D14" s="8" t="n"/>
+        <v>9373.199999999999</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -710,217 +641,217 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.77734375" defaultRowHeight="20.4" customHeight="1"/>
   <sheetData>
     <row r="1" ht="20.4" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>MONTH</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>COST (TL)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>COST(USD)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20.4" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>30.05</v>
+      <c r="B2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>35.6</v>
       </c>
     </row>
     <row r="3" ht="20.4" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>30.7</v>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>36.24</v>
       </c>
     </row>
     <row r="4" ht="20.4" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>32.12</v>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>37.06</v>
       </c>
     </row>
     <row r="5" ht="20.4" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>32.4</v>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>38.08</v>
       </c>
     </row>
     <row r="6" ht="20.4" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>148420.28</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>4605.04</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>32.23</v>
+      <c r="B6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>38.68</v>
       </c>
     </row>
     <row r="7" ht="20.4" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>June</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>32.46</v>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>39.52</v>
       </c>
     </row>
     <row r="8" ht="20.4" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>33.04</v>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>40.27</v>
       </c>
     </row>
     <row r="9" ht="20.4" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>August</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>179012.37</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>5330.92</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>33.58</v>
+      <c r="B9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>40.88</v>
       </c>
     </row>
     <row r="10" ht="20.4" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>September</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
+      <c r="B10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>41.26</v>
       </c>
     </row>
     <row r="11" ht="20.4" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>41.71</v>
       </c>
     </row>
     <row r="12" ht="20.4" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>42.34</v>
       </c>
     </row>
     <row r="13" ht="20.4" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>December</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
+      <c r="B13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>42.75</v>
       </c>
     </row>
     <row r="14" ht="20.4" customHeight="1">
@@ -930,12 +861,12 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>327432.65</v>
+        <v>0</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>9935.959999999999</v>
-      </c>
-      <c r="D14" s="8" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -952,217 +883,217 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.77734375" defaultRowHeight="20.4" customHeight="1"/>
   <sheetData>
     <row r="1" ht="20.4" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>MONTH</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>COST (TL)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>COST(USD)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20.4" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>327162.16</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>10887.26</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>30.05</v>
+      <c r="B2" s="2" t="n">
+        <v>353785.79</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>9937.799999999999</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>35.6</v>
       </c>
     </row>
     <row r="3" ht="20.4" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>327162.16</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>10656.75</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>30.7</v>
+      <c r="B3" s="2" t="n">
+        <v>354764.5</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>9789.309999999999</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>36.24</v>
       </c>
     </row>
     <row r="4" ht="20.4" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>327162.16</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>10185.62</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>32.12</v>
+      <c r="B4" s="2" t="n">
+        <v>360410.36</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9725.049999999999</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>37.06</v>
       </c>
     </row>
     <row r="5" ht="20.4" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>327162.16</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>10097.6</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>32.4</v>
+      <c r="B5" s="2" t="n">
+        <v>376047.72</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>9875.200000000001</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>38.08</v>
       </c>
     </row>
     <row r="6" ht="20.4" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>327162.16</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>10150.86</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>32.23</v>
+      <c r="B6" s="2" t="n">
+        <v>379498.8</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>9811.24</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>38.68</v>
       </c>
     </row>
     <row r="7" ht="20.4" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>June</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>327162.16</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>10078.93</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>32.46</v>
+      <c r="B7" s="2" t="n">
+        <v>386871.84</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>9789.27</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>39.52</v>
       </c>
     </row>
     <row r="8" ht="20.4" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>336754.38</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>10192.32</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>33.04</v>
+      <c r="B8" s="2" t="n">
+        <v>386871.84</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>9606.950000000001</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>40.27</v>
       </c>
     </row>
     <row r="9" ht="20.4" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>August</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>336754.38</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>10028.42</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>33.58</v>
+      <c r="B9" s="2" t="n">
+        <v>386871.84</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>9463.6</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>40.88</v>
       </c>
     </row>
     <row r="10" ht="20.4" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>September</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
+      <c r="B10" s="2" t="n">
+        <v>386871.84</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>9376.440000000001</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>41.26</v>
       </c>
     </row>
     <row r="11" ht="20.4" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="n">
+        <v>386871.84</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>9275.280000000001</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>41.71</v>
       </c>
     </row>
     <row r="12" ht="20.4" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
+      <c r="B12" s="2" t="n">
+        <v>390000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>9211.15</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>42.34</v>
       </c>
     </row>
     <row r="13" ht="20.4" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>December</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
+      <c r="B13" s="2" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>9356.73</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>42.75</v>
       </c>
     </row>
     <row r="14" ht="20.4" customHeight="1">
@@ -1172,12 +1103,12 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>2636481.72</v>
+        <v>4548866.369999999</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>82277.75999999999</v>
-      </c>
-      <c r="D14" s="8" t="n"/>
+        <v>115218.02</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1194,217 +1125,217 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.77734375" defaultRowHeight="20.4" customHeight="1"/>
   <sheetData>
     <row r="1" ht="20.4" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>MONTH</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>COST (TL)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>COST(USD)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20.4" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
+      <c r="B2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>35.6</v>
       </c>
     </row>
     <row r="3" ht="20.4" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>36.24</v>
       </c>
     </row>
     <row r="4" ht="20.4" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>37.06</v>
       </c>
     </row>
     <row r="5" ht="20.4" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>38.08</v>
       </c>
     </row>
     <row r="6" ht="20.4" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
+      <c r="B6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>38.68</v>
       </c>
     </row>
     <row r="7" ht="20.4" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>June</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
+      <c r="B7" s="2" t="n">
+        <v>13951</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>353.01</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>39.52</v>
       </c>
     </row>
     <row r="8" ht="20.4" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>40.27</v>
       </c>
     </row>
     <row r="9" ht="20.4" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>August</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>-22961.59</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>-667.49</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>34.4</v>
+      <c r="B9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>40.88</v>
       </c>
     </row>
     <row r="10" ht="20.4" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>September</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
+      <c r="B10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>41.26</v>
       </c>
     </row>
     <row r="11" ht="20.4" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>41.71</v>
       </c>
     </row>
     <row r="12" ht="20.4" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>42.34</v>
       </c>
     </row>
     <row r="13" ht="20.4" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>December</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
+      <c r="B13" s="2" t="n">
+        <v>47000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1099.42</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>42.75</v>
       </c>
     </row>
     <row r="14" ht="20.4" customHeight="1">
@@ -1414,12 +1345,12 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>-22961.59</v>
+        <v>60951</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-667.49</v>
-      </c>
-      <c r="D14" s="9" t="n"/>
+        <v>1452.43</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1436,217 +1367,217 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.77734375" defaultRowHeight="20.4" customHeight="1"/>
   <sheetData>
     <row r="1" ht="20.4" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>MONTH</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>COST (TL)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>COST(USD)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20.4" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>379.37</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>30.05</v>
+      <c r="B2" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>183.41</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>35.6</v>
       </c>
     </row>
     <row r="3" ht="20.4" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>371.34</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>30.7</v>
+      <c r="B3" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>179.86</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>36.24</v>
       </c>
     </row>
     <row r="4" ht="20.4" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>354.92</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>32.12</v>
+      <c r="B4" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>175.39</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>37.06</v>
       </c>
     </row>
     <row r="5" ht="20.4" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>351.85</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>32.4</v>
+      <c r="B5" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>170.69</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>38.08</v>
       </c>
     </row>
     <row r="6" ht="20.4" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>353.71</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>32.23</v>
+      <c r="B6" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>168.05</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>38.68</v>
       </c>
     </row>
     <row r="7" ht="20.4" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>June</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>351.2</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>32.46</v>
+      <c r="B7" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>164.47</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>39.52</v>
       </c>
     </row>
     <row r="8" ht="20.4" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>345.04</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>33.04</v>
+      <c r="B8" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>161.41</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>40.27</v>
       </c>
     </row>
     <row r="9" ht="20.4" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>August</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>339.49</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>33.58</v>
+      <c r="B9" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>40.88</v>
       </c>
     </row>
     <row r="10" ht="20.4" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>September</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
+      <c r="B10" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>157.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>41.26</v>
       </c>
     </row>
     <row r="11" ht="20.4" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>155.84</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>41.71</v>
       </c>
     </row>
     <row r="12" ht="20.4" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>42.34</v>
       </c>
     </row>
     <row r="13" ht="20.4" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>December</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
+      <c r="B13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>42.75</v>
       </c>
     </row>
     <row r="14" ht="20.4" customHeight="1">
@@ -1656,12 +1587,254 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>91200</v>
+        <v>65000</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2846.92</v>
-      </c>
-      <c r="D14" s="8" t="n"/>
+        <v>1675.66</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.77734375" defaultRowHeight="19.2" customHeight="1"/>
+  <sheetData>
+    <row r="1" ht="19.2" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>MONTH</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>COST (TL)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>COST(USD)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="19.2" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>259.15</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="3" ht="19.2" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>254.57</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>36.24</v>
+      </c>
+    </row>
+    <row r="4" ht="19.2" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>248.25</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>37.06</v>
+      </c>
+    </row>
+    <row r="5" ht="19.2" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>241.6</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>38.08</v>
+      </c>
+    </row>
+    <row r="6" ht="19.2" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>237.85</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>38.68</v>
+      </c>
+    </row>
+    <row r="7" ht="19.2" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>232.79</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>39.52</v>
+      </c>
+    </row>
+    <row r="8" ht="19.2" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>228.46</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>40.27</v>
+      </c>
+    </row>
+    <row r="9" ht="19.2" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>232.79</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>40.88</v>
+      </c>
+    </row>
+    <row r="10" ht="19.2" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>222.98</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>41.26</v>
+      </c>
+    </row>
+    <row r="11" ht="19.2" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>220.57</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>41.71</v>
+      </c>
+    </row>
+    <row r="12" ht="19.2" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>217.29</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>42.34</v>
+      </c>
+    </row>
+    <row r="13" ht="19.2" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>215.2</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>42.75</v>
+      </c>
+    </row>
+    <row r="14" ht="19.2" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>110400</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>2811.5</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
